--- a/Testing_Data/PressureSensorCalibration.xlsx
+++ b/Testing_Data/PressureSensorCalibration.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7200BF-30DC-46F1-AD44-5040427BA7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BA3EDF-C44A-4987-9AA4-E53457F352CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26010" yWindow="0" windowWidth="17130" windowHeight="15435" xr2:uid="{ED23B71C-6DC7-4F03-A302-FE33CB0246DD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{ED23B71C-6DC7-4F03-A302-FE33CB0246DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>Voltage (V)</t>
   </si>
@@ -41,11 +52,20 @@
   <si>
     <t>Sample</t>
   </si>
+  <si>
+    <t>serial reading</t>
+  </si>
+  <si>
+    <t>pressure(kPA)</t>
+  </si>
+  <si>
+    <t>Moe's tests</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -91,7 +111,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0C37CB85-D3A6-4DF8-8F83-1B390F3EF514}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -434,6 +456,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -441,7 +464,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -777,6 +799,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -784,7 +807,418 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>pressure(kPA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.36417082239720033"/>
+                  <c:y val="-1.4305555555555556E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$30:$A$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>347</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>412</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>527</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>677</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>817</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>827</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$30:$B$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>620</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7508-47AA-B567-50DA72A7C942}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1085243503"/>
+        <c:axId val="1059663151"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1085243503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1059663151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1059663151"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1085243503"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -899,6 +1333,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1416,6 +1890,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1936,15 +2926,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>403225</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>98425</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2005,13 +2995,49 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>377825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>73025</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09307B6A-466B-8F9E-5FA4-3302305C25AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2049,7 +3075,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2155,7 +3181,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2297,7 +3323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2305,14 +3331,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07EB23B-8D5C-452B-917B-439C5A6B7860}">
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,7 +3352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0.83579999999999999</v>
       </c>
@@ -2340,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2.0674000000000001</v>
       </c>
@@ -2354,7 +3380,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2.7370000000000001</v>
       </c>
@@ -2362,7 +3388,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3.4163999999999999</v>
       </c>
@@ -2370,7 +3396,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4.0468999999999999</v>
       </c>
@@ -2378,7 +3404,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4.6481000000000003</v>
       </c>
@@ -2386,7 +3412,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4.7897999999999996</v>
       </c>
@@ -2394,12 +3420,12 @@
         <v>620</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>2</v>
       </c>
@@ -2410,7 +3436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>0.83579999999999999</v>
       </c>
@@ -2425,7 +3451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>4.7702999999999998</v>
       </c>
@@ -2441,13 +3467,90 @@
         <v>-6.5600000000074488E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N26">
         <v>4.7214</v>
       </c>
       <c r="O26">
         <f>156.8*N26-131.06</f>
         <v>609.25552000000016</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>32</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>265</v>
+      </c>
+      <c r="B31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>347</v>
+      </c>
+      <c r="B32">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>412</v>
+      </c>
+      <c r="B33">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>527</v>
+      </c>
+      <c r="B34">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>677</v>
+      </c>
+      <c r="B35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>817</v>
+      </c>
+      <c r="B36">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>827</v>
+      </c>
+      <c r="B37">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
